--- a/Hoja de trabajo - 4.5% UDI.xlsx
+++ b/Hoja de trabajo - 4.5% UDI.xlsx
@@ -131,7 +131,7 @@
     <t>EXENCION DE PAGO DE PRIMAS</t>
   </si>
   <si>
-    <t>ANTONIO</t>
+    <t>ORVI</t>
   </si>
   <si>
     <t>15 AÑOS</t>
